--- a/artfynd/A 15189-2022 artfynd.xlsx
+++ b/artfynd/A 15189-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128803409</v>
       </c>
       <c r="B2" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15189-2022 artfynd.xlsx
+++ b/artfynd/A 15189-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128803409</v>
       </c>
       <c r="B2" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15189-2022 artfynd.xlsx
+++ b/artfynd/A 15189-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128803409</v>
       </c>
       <c r="B2" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15189-2022 artfynd.xlsx
+++ b/artfynd/A 15189-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128803409</v>
       </c>
       <c r="B2" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15189-2022 artfynd.xlsx
+++ b/artfynd/A 15189-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128803409</v>
       </c>
       <c r="B2" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15189-2022 artfynd.xlsx
+++ b/artfynd/A 15189-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128803409</v>
       </c>
       <c r="B2" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15189-2022 artfynd.xlsx
+++ b/artfynd/A 15189-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128803409</v>
       </c>
       <c r="B2" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15189-2022 artfynd.xlsx
+++ b/artfynd/A 15189-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128803409</v>
       </c>
       <c r="B2" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15189-2022 artfynd.xlsx
+++ b/artfynd/A 15189-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128803409</v>
       </c>
       <c r="B2" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15189-2022 artfynd.xlsx
+++ b/artfynd/A 15189-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128803409</v>
       </c>
       <c r="B2" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15189-2022 artfynd.xlsx
+++ b/artfynd/A 15189-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128803409</v>
       </c>
       <c r="B2" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15189-2022 artfynd.xlsx
+++ b/artfynd/A 15189-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128803409</v>
       </c>
       <c r="B2" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
